--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2738,48 +2738,60 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>82122432</v>
+        <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>5199</v>
+        <v>58169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ehrendals kvarn, SV, Srm</t>
+          <t>Ehrendal, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631329</v>
+        <v>631271</v>
       </c>
       <c r="R22" t="n">
-        <v>6539504</v>
+        <v>6539364</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2803,12 +2815,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-10-12</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2823,65 +2845,62 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Peter Lantz</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Peter Lantz</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82122432</t>
+          <t>https://artportalen.se/Sighting/137113891</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>82122426</v>
+        <v>82122432</v>
       </c>
       <c r="B23" t="n">
-        <v>92329</v>
+        <v>5199</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6040186</v>
+        <v>105930</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kötticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ehrendals kvarn, SV, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>631265</v>
+        <v>631329</v>
       </c>
       <c r="R23" t="n">
-        <v>6539420</v>
+        <v>6539504</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2916,18 +2935,12 @@
           <t>2019-10-12</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2944,6 +2957,117 @@
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82122432</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>82122426</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ehrendals kvarn, SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>631265</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6539420</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2019-10-12</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/82122426</t>
         </is>
@@ -2973,6 +3097,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2773,11 +2773,7 @@
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 15285-2022 artfynd.xlsx
+++ b/artfynd/A 15285-2022 artfynd.xlsx
@@ -2741,7 +2741,7 @@
         <v>137113891</v>
       </c>
       <c r="B22" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
